--- a/output/graficos_dimensiones/comunal_e_matricula_a_2022_o_higgins.xlsx
+++ b/output/graficos_dimensiones/comunal_e_matricula_a_2022_o_higgins.xlsx
@@ -153,7 +153,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 22:25</t>
+    <t xml:space="preserve">2026-09-10 01:40</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_e_matricula_a_2022_o_higgins.xlsx
+++ b/output/graficos_dimensiones/comunal_e_matricula_a_2022_o_higgins.xlsx
@@ -153,7 +153,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-10 01:40</t>
+    <t xml:space="preserve">2026-09-18 11:36</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_e_matricula_a_2022_o_higgins.xlsx
+++ b/output/graficos_dimensiones/comunal_e_matricula_a_2022_o_higgins.xlsx
@@ -153,7 +153,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 11:36</t>
+    <t xml:space="preserve">2026-09-23 15:41</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_e_matricula_a_2022_o_higgins.xlsx
+++ b/output/graficos_dimensiones/comunal_e_matricula_a_2022_o_higgins.xlsx
@@ -105,7 +105,7 @@
     <t xml:space="preserve">Litueche</t>
   </si>
   <si>
-    <t xml:space="preserve">Marchihue</t>
+    <t xml:space="preserve">Marchigüe</t>
   </si>
   <si>
     <t xml:space="preserve">Navidad</t>
@@ -153,7 +153,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-23 15:41</t>
+    <t xml:space="preserve">2026-10-04 10:49</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_e_matricula_a_2022_o_higgins.xlsx
+++ b/output/graficos_dimensiones/comunal_e_matricula_a_2022_o_higgins.xlsx
@@ -153,7 +153,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-04 10:49</t>
+    <t xml:space="preserve">2026-10-05 16:57</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -1413,7 +1413,7 @@
         <v>100.57</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>103</v>
+        <v>103.01</v>
       </c>
       <c r="I30" s="2" t="n">
         <v>49.43</v>
